--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0123.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0123.xlsx
@@ -2329,7 +2329,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Ta sẽ tiêu diệt Sigillum. Vậy nên, r?i ?i. Tránh xa nó ra, được không?</t>
+          <t>Ta sẽ tiêu diệt Sigillum. Vậy nên, Rời đi. Tránh xa nó ra, được không?</t>
         </is>
       </c>
     </row>
